--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8095238095238095</v>
+        <v>0.8863636363636364</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6197183098591549</v>
+        <v>0.7112676056338029</v>
       </c>
       <c r="D2">
-        <v>0.4426229508196721</v>
+        <v>0.3445378151260504</v>
       </c>
       <c r="E2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
